--- a/data/controles_results/dif_medias/controls_staggered_vars/difmedias_controles_staggered_variables_2017_T4_0.xlsx
+++ b/data/controles_results/dif_medias/controls_staggered_vars/difmedias_controles_staggered_variables_2017_T4_0.xlsx
@@ -45,7 +45,7 @@
     <t>N</t>
   </si>
   <si>
-    <t>91</t>
+    <t>87</t>
   </si>
   <si>
     <t xml:space="preserve"> (1) </t>
@@ -57,40 +57,40 @@
     <t>Mean/(SE)</t>
   </si>
   <si>
-    <t>0.275</t>
-  </si>
-  <si>
-    <t>(0.047)</t>
-  </si>
-  <si>
-    <t>0.462</t>
-  </si>
-  <si>
-    <t>(0.053)</t>
-  </si>
-  <si>
-    <t>0.176</t>
-  </si>
-  <si>
-    <t>(0.040)</t>
-  </si>
-  <si>
-    <t>0.681</t>
-  </si>
-  <si>
-    <t>(0.193)</t>
-  </si>
-  <si>
-    <t>1.110</t>
-  </si>
-  <si>
-    <t>(0.187)</t>
-  </si>
-  <si>
-    <t>0.220</t>
-  </si>
-  <si>
-    <t>(0.060)</t>
+    <t>0.287</t>
+  </si>
+  <si>
+    <t>(0.049)</t>
+  </si>
+  <si>
+    <t>0.483</t>
+  </si>
+  <si>
+    <t>(0.054)</t>
+  </si>
+  <si>
+    <t>0.184</t>
+  </si>
+  <si>
+    <t>(0.042)</t>
+  </si>
+  <si>
+    <t>0.713</t>
+  </si>
+  <si>
+    <t>(0.201)</t>
+  </si>
+  <si>
+    <t>1.161</t>
+  </si>
+  <si>
+    <t>(0.194)</t>
+  </si>
+  <si>
+    <t>0.230</t>
+  </si>
+  <si>
+    <t>(0.063)</t>
   </si>
   <si>
     <t>23</t>
@@ -138,7 +138,7 @@
     <t>(0.170)</t>
   </si>
   <si>
-    <t>114</t>
+    <t>110</t>
   </si>
   <si>
     <t>(2)-(1)</t>
@@ -150,22 +150,22 @@
     <t>Mean difference</t>
   </si>
   <si>
-    <t>0.247**</t>
-  </si>
-  <si>
-    <t>0.365***</t>
-  </si>
-  <si>
-    <t>0.476***</t>
-  </si>
-  <si>
-    <t>0.971</t>
-  </si>
-  <si>
-    <t>2.064***</t>
-  </si>
-  <si>
-    <t>0.650***</t>
+    <t>0.234**</t>
+  </si>
+  <si>
+    <t>0.343***</t>
+  </si>
+  <si>
+    <t>0.468***</t>
+  </si>
+  <si>
+    <t>0.940</t>
+  </si>
+  <si>
+    <t>2.013***</t>
+  </si>
+  <si>
+    <t>0.640***</t>
   </si>
 </sst>
 </file>
